--- a/outputs/daily/hr_rankings_2026-10-07.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-07.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>38.8</v>
       </c>
       <c r="R2" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -1106,34 +1106,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2510,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3263,56 +3255,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sean Newcomb</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>656794</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,61 +3306,65 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>53.3</v>
+        <v>57.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>28.5</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
-        <v>50.6</v>
+        <v>22.6</v>
       </c>
       <c r="S11" t="n">
-        <v>94.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
-        <v>34.9</v>
+        <v>74.2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3397,142 +3381,110 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>104.4475</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4964</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2079</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>57.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1874</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>88.76</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.3761</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1236</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>22.19</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>0.1801</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3543,24 +3495,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-07T20:00:00Z</t>
@@ -3573,26 +3525,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Sean Newcomb</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>656794</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3606,26 +3558,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>38.8</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>41.2</v>
+        <v>34.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3639,7 +3591,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3660,7 +3612,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3682,7 +3634,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3692,112 +3644,112 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.1212</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4693</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3603</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3761</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -3823,44 +3775,56 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Daniel Espino</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>682982</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>53.9</v>
+        <v>53.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3874,65 +3838,61 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="n">
+        <v>50</v>
+      </c>
+      <c r="U13" t="n">
         <v>41.2</v>
       </c>
-      <c r="R13" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>60</v>
-      </c>
-      <c r="U13" t="n">
-        <v>74.2</v>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3949,110 +3909,142 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>104.4475</t>
+          <t>100.1212</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4964</t>
+          <t>0.4693</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2079</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3603</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1801</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.2069</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>36.4</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.317</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.135</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4154,34 +4146,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4396,7 +4384,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4420,7 +4408,7 @@
         <v>38.8</v>
       </c>
       <c r="R15" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -4718,34 +4706,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5562,34 +5546,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6872,7 +6852,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6896,7 +6876,7 @@
         <v>38.8</v>
       </c>
       <c r="R24" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S24" t="n">
         <v>52.4</v>
@@ -7952,7 +7932,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -7976,7 +7956,7 @@
         <v>28.5</v>
       </c>
       <c r="R28" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S28" t="n">
         <v>96.59999999999999</v>
@@ -8232,7 +8212,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>46.8</v>
+        <v>46.5</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8256,7 +8236,7 @@
         <v>38.8</v>
       </c>
       <c r="R29" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S29" t="n">
         <v>44.8</v>
@@ -8554,34 +8534,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9299,47 +9275,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T00:00:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9362,61 +9338,65 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>18.8</v>
+        <v>30.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>38.8</v>
+        <v>34.3</v>
       </c>
       <c r="R33" t="n">
-        <v>50.6</v>
+        <v>38.2</v>
       </c>
       <c r="S33" t="n">
-        <v>93.2</v>
+        <v>95.5</v>
       </c>
       <c r="T33" t="n">
         <v>80</v>
       </c>
       <c r="U33" t="n">
-        <v>43.1</v>
+        <v>18.3</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9433,142 +9413,134 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>97.5005</t>
+          <t>98.5475</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>39.4</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9579,47 +9551,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-08T00:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9628,7 +9600,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9642,65 +9614,61 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>30.5</v>
+        <v>18.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>34.3</v>
+        <v>38.8</v>
       </c>
       <c r="R34" t="n">
-        <v>38.2</v>
+        <v>48.6</v>
       </c>
       <c r="S34" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T34" t="n">
         <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>18.3</v>
+        <v>43.1</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9717,134 +9685,142 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>98.5475</t>
+          <t>97.5005</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.348</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr"/>
-      <c r="BH34" t="inlineStr"/>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -10696,7 +10672,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10720,7 +10696,7 @@
         <v>28.1</v>
       </c>
       <c r="R38" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S38" t="n">
         <v>100</v>
@@ -12052,7 +12028,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12076,7 +12052,7 @@
         <v>28.5</v>
       </c>
       <c r="R43" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S43" t="n">
         <v>86.40000000000001</v>
@@ -12835,27 +12811,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12865,17 +12841,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -12884,7 +12860,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -12902,22 +12878,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>24</v>
+        <v>33.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>38.5</v>
+        <v>37.3</v>
       </c>
       <c r="R46" t="n">
-        <v>50.6</v>
+        <v>48.9</v>
       </c>
       <c r="S46" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T46" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U46" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -12931,7 +12907,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -12952,7 +12928,7 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -12969,7 +12945,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
@@ -12984,112 +12960,112 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
@@ -13099,12 +13075,12 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13115,27 +13091,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -13145,17 +13121,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -13164,7 +13140,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -13182,22 +13158,22 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>33.9</v>
+        <v>24</v>
       </c>
       <c r="Q47" t="n">
-        <v>37.3</v>
+        <v>38.5</v>
       </c>
       <c r="R47" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="S47" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T47" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U47" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -13206,37 +13182,33 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr"/>
@@ -13253,7 +13225,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -13268,112 +13240,112 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
@@ -13383,12 +13355,12 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr"/>
@@ -13490,34 +13462,30 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14324,28 +14292,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y51" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14560,7 +14532,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14584,7 +14556,7 @@
         <v>38.8</v>
       </c>
       <c r="R52" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S52" t="n">
         <v>86.40000000000001</v>
@@ -14840,7 +14812,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -14864,7 +14836,7 @@
         <v>28.1</v>
       </c>
       <c r="R53" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S53" t="n">
         <v>52.4</v>
@@ -15120,7 +15092,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15144,7 +15116,7 @@
         <v>28.1</v>
       </c>
       <c r="R54" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S54" t="n">
         <v>76.2</v>
@@ -15924,7 +15896,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -15948,7 +15920,7 @@
         <v>38.8</v>
       </c>
       <c r="R57" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S57" t="n">
         <v>76.2</v>
@@ -16772,7 +16744,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -16796,7 +16768,7 @@
         <v>28.5</v>
       </c>
       <c r="R60" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S60" t="n">
         <v>64.3</v>
@@ -17052,7 +17024,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -17076,7 +17048,7 @@
         <v>28.1</v>
       </c>
       <c r="R61" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S61" t="n">
         <v>44.8</v>
@@ -17332,7 +17304,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>35.1</v>
+        <v>34.8</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17356,7 +17328,7 @@
         <v>28.5</v>
       </c>
       <c r="R62" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S62" t="n">
         <v>93.2</v>
@@ -20866,7 +20838,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -20890,7 +20862,7 @@
         <v>38.8</v>
       </c>
       <c r="R2" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -21188,34 +21160,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22592,34 +22560,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23345,56 +23309,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sean Newcomb</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>656794</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -23408,61 +23360,65 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>53.3</v>
+        <v>57.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>28.5</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
-        <v>50.6</v>
+        <v>22.6</v>
       </c>
       <c r="S11" t="n">
-        <v>94.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
-        <v>34.9</v>
+        <v>74.2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -23479,142 +23435,110 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>104.4475</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4964</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2079</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>57.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1874</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>88.76</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.3761</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1236</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>22.19</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>0.1801</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -23625,24 +23549,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-07T20:00:00Z</t>
@@ -23655,26 +23579,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Sean Newcomb</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>656794</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -23688,26 +23612,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>38.8</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>41.2</v>
+        <v>34.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -23721,7 +23645,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -23742,7 +23666,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -23764,7 +23688,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -23774,112 +23698,112 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.1212</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4693</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3603</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3761</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -23905,44 +23829,56 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Daniel Espino</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>682982</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>53.9</v>
+        <v>53.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -23956,65 +23892,61 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="n">
+        <v>50</v>
+      </c>
+      <c r="U13" t="n">
         <v>41.2</v>
       </c>
-      <c r="R13" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>60</v>
-      </c>
-      <c r="U13" t="n">
-        <v>74.2</v>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -24031,110 +23963,142 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>104.4475</t>
+          <t>100.1212</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4964</t>
+          <t>0.4693</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2079</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3603</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1801</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.2069</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>36.4</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.317</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.135</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -24236,34 +24200,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24478,7 +24438,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -24502,7 +24462,7 @@
         <v>38.8</v>
       </c>
       <c r="R15" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -24800,34 +24760,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25644,34 +25600,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-10-07.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-07.xlsx
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>58.8</v>
+        <v>59.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1371,7 +1371,7 @@
         <v>48.9</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1381,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2161,7 +2157,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2180,7 +2176,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>56.9</v>
+        <v>56.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2194,7 +2190,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2207,7 +2203,7 @@
         <v>48.9</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2217,39 +2213,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2415,24 +2407,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -2445,17 +2437,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2464,7 +2456,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.2</v>
+        <v>56.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,26 +2470,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>51.1</v>
+        <v>58.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.3</v>
+        <v>35.6</v>
       </c>
       <c r="R8" t="n">
         <v>48.9</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2511,7 +2503,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2549,127 +2541,127 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>102.9585</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2695,24 +2687,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -2725,17 +2717,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2744,7 +2736,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2758,62 +2750,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="R9" t="n">
         <v>48.9</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>53.3</v>
+        <v>100</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2833,127 +2821,127 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9585</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4335,27 +4323,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4365,17 +4353,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4384,7 +4372,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4398,26 +4386,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>37</v>
+        <v>45.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.8</v>
+        <v>35.6</v>
       </c>
       <c r="R15" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="S15" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>44.1</v>
+        <v>32</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4431,7 +4419,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4452,7 +4440,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4469,127 +4457,127 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>46.98</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -4599,12 +4587,12 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4615,27 +4603,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4645,17 +4633,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4664,7 +4652,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4678,26 +4666,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>39.3</v>
+        <v>37</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.3</v>
+        <v>38.8</v>
       </c>
       <c r="R16" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>13</v>
+        <v>44.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4711,7 +4699,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4732,7 +4720,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4749,127 +4737,127 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>40.12</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>29.94</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>0.1471</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
           <t>36.4</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>26.93</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.1615</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>7.16</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -4879,12 +4867,12 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4895,24 +4883,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -4925,17 +4913,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4944,7 +4932,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4958,62 +4946,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>45.1</v>
+        <v>39.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="R17" t="n">
         <v>48.9</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5033,12 +5017,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5048,12 +5032,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5063,97 +5047,97 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -7648,7 +7632,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7662,7 +7646,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -7675,7 +7659,7 @@
         <v>48.9</v>
       </c>
       <c r="S27" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T27" t="n">
         <v>50</v>
@@ -7685,39 +7669,35 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8443,24 +8423,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -8473,17 +8453,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8492,7 +8472,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8506,26 +8486,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>32.7</v>
+        <v>34.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>37.3</v>
+        <v>35.6</v>
       </c>
       <c r="R30" t="n">
         <v>48.9</v>
       </c>
       <c r="S30" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T30" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U30" t="n">
-        <v>29.2</v>
+        <v>24</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8539,7 +8519,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8577,12 +8557,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8592,12 +8572,12 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8607,97 +8587,97 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
@@ -8723,47 +8703,47 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-08T00:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8772,7 +8752,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8786,62 +8766,58 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>42.2</v>
+        <v>32.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>34.3</v>
+        <v>37.3</v>
       </c>
       <c r="R31" t="n">
-        <v>38.2</v>
+        <v>48.9</v>
       </c>
       <c r="S31" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T31" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>14.6</v>
+        <v>29.2</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8866,22 +8842,22 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -8891,87 +8867,87 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>100.4248</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.4005</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3093</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -8981,14 +8957,22 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr"/>
-      <c r="BH31" t="inlineStr"/>
+          <t>26.63</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -8999,27 +8983,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jazz Chisholm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-08T00:00:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9029,17 +9013,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9062,26 +9046,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>39.5</v>
+        <v>42.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>43.4</v>
+        <v>34.3</v>
       </c>
       <c r="R32" t="n">
-        <v>22.6</v>
+        <v>38.2</v>
       </c>
       <c r="S32" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>37.8</v>
+        <v>14.6</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9095,7 +9079,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9137,27 +9121,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9167,104 +9151,104 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.4248</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4005</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3093</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr"/>
       <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9275,27 +9259,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-08T00:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9305,17 +9289,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9324,7 +9308,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>45.5</v>
+        <v>45.9</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9338,26 +9322,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>30.5</v>
+        <v>39.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>34.3</v>
+        <v>43.4</v>
       </c>
       <c r="R33" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S33" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T33" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>18.3</v>
+        <v>37.8</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9371,7 +9355,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -9413,12 +9397,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -9428,12 +9412,12 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9443,104 +9427,104 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>98.5475</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9551,47 +9535,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T00:00:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9600,7 +9584,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9614,61 +9598,65 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>18.8</v>
+        <v>30.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>38.8</v>
+        <v>34.3</v>
       </c>
       <c r="R34" t="n">
-        <v>48.6</v>
+        <v>38.2</v>
       </c>
       <c r="S34" t="n">
-        <v>93.2</v>
+        <v>95.5</v>
       </c>
       <c r="T34" t="n">
         <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>43.1</v>
+        <v>18.3</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9685,142 +9673,134 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>97.5005</t>
+          <t>98.5475</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>39.4</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9831,47 +9811,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-08T00:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9894,65 +9874,61 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>47.4</v>
+        <v>18.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>34.3</v>
+        <v>38.8</v>
       </c>
       <c r="R35" t="n">
-        <v>38.2</v>
+        <v>48.6</v>
       </c>
       <c r="S35" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T35" t="n">
         <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>43.1</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -9969,12 +9945,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -9984,119 +9960,127 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>100.7514</t>
+          <t>97.5005</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4497</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.2038</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.348</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>70.79</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10107,27 +10091,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-08T00:00:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10137,14 +10121,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L36" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10158,26 +10154,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>40.6</v>
+        <v>47.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R36" t="n">
-        <v>22.6</v>
+        <v>38.2</v>
       </c>
       <c r="S36" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T36" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10191,7 +10187,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10216,7 +10212,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10233,12 +10229,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10248,12 +10244,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10263,80 +10259,104 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>100.8422</t>
+          <t>100.7514</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4497</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1709</t>
+          <t>0.2038</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3273</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>70.79</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1758</t>
-        </is>
-      </c>
-      <c r="BA36" t="inlineStr"/>
-      <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
-      <c r="BF36" t="inlineStr"/>
+          <t>0.1975</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10347,24 +10367,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>2026-10-08T02:00:00Z</t>
@@ -10377,26 +10397,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Walker Buehler</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>621111</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10410,26 +10418,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>38.2</v>
+        <v>40.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>43.4</v>
+        <v>41.2</v>
       </c>
       <c r="R37" t="n">
         <v>22.6</v>
       </c>
       <c r="S37" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T37" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U37" t="n">
-        <v>25.3</v>
+        <v>5.1</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10443,7 +10451,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -10468,7 +10476,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -10490,22 +10498,22 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10515,99 +10523,75 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.8422</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1709</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3273</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BA37" t="inlineStr">
-        <is>
-          <t>8.73</t>
-        </is>
-      </c>
-      <c r="BB37" t="inlineStr">
-        <is>
-          <t>38.43</t>
-        </is>
-      </c>
-      <c r="BC37" t="inlineStr">
-        <is>
-          <t>88.88</t>
-        </is>
-      </c>
-      <c r="BD37" t="inlineStr">
-        <is>
-          <t>0.4164</t>
-        </is>
-      </c>
-      <c r="BE37" t="inlineStr">
-        <is>
-          <t>0.1645</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>23.44</t>
-        </is>
-      </c>
+          <t>0.1758</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr">
@@ -10623,56 +10607,56 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Sean Newcomb</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>656794</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>44.5</v>
+        <v>44.9</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10686,58 +10670,62 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>25.8</v>
+        <v>38.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>28.1</v>
+        <v>43.4</v>
       </c>
       <c r="R38" t="n">
-        <v>48.6</v>
+        <v>22.6</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>71.7</v>
       </c>
       <c r="T38" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U38" t="n">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10757,27 +10745,27 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -10787,112 +10775,104 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.3761</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1236</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>22.19</t>
-        </is>
-      </c>
-      <c r="BG38" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH38" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>23.44</t>
+        </is>
+      </c>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -10903,27 +10883,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -10933,26 +10913,26 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Sean Newcomb</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>656794</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>44.1</v>
+        <v>44.5</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -10966,62 +10946,58 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>34.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>35.6</v>
+        <v>28.1</v>
       </c>
       <c r="R39" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="S39" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T39" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U39" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11041,27 +11017,27 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -11071,97 +11047,97 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3761</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
@@ -11171,12 +11147,12 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr"/>
@@ -15323,42 +15299,54 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Tyler Glasnow</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>607192</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L55" t="n">
         <v>40.8</v>
       </c>
@@ -15374,65 +15362,61 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>28.7</v>
+        <v>15.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>41.2</v>
+        <v>34.7</v>
       </c>
       <c r="R55" t="n">
-        <v>22.6</v>
+        <v>48.9</v>
       </c>
       <c r="S55" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U55" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr"/>
@@ -15449,27 +15433,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15479,80 +15463,112 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>100.2761</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.3871</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1175</t>
-        </is>
-      </c>
-      <c r="BA55" t="inlineStr"/>
-      <c r="BB55" t="inlineStr"/>
-      <c r="BC55" t="inlineStr"/>
-      <c r="BD55" t="inlineStr"/>
-      <c r="BE55" t="inlineStr"/>
-      <c r="BF55" t="inlineStr"/>
-      <c r="BG55" t="inlineStr"/>
-      <c r="BH55" t="inlineStr"/>
+          <t>0.146</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>0.3296</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
+        <is>
+          <t>0.1357</t>
+        </is>
+      </c>
+      <c r="BF55" t="inlineStr">
+        <is>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15563,56 +15579,44 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Tyler Glasnow</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>607192</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>40.1</v>
+        <v>40.8</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15626,26 +15630,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>15.3</v>
+        <v>28.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>34.7</v>
+        <v>41.2</v>
       </c>
       <c r="R56" t="n">
-        <v>48.9</v>
+        <v>22.6</v>
       </c>
       <c r="S56" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T56" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>52.8</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15659,7 +15663,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15684,7 +15688,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -15701,27 +15705,27 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15731,112 +15735,80 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>100.2761</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3871</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="BA56" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="BB56" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="BC56" t="inlineStr">
-        <is>
-          <t>89.53</t>
-        </is>
-      </c>
-      <c r="BD56" t="inlineStr">
-        <is>
-          <t>0.3296</t>
-        </is>
-      </c>
-      <c r="BE56" t="inlineStr">
-        <is>
-          <t>0.1357</t>
-        </is>
-      </c>
-      <c r="BF56" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH56" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>0.1175</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16176,7 +16148,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>37.4</v>
+        <v>38</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16190,7 +16162,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -16203,7 +16175,7 @@
         <v>48.9</v>
       </c>
       <c r="S58" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T58" t="n">
         <v>50</v>
@@ -16213,39 +16185,35 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16416,7 +16384,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -16441,7 +16409,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -16460,7 +16428,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>36.3</v>
+        <v>35.3</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -16474,7 +16442,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -16487,7 +16455,7 @@
         <v>48.9</v>
       </c>
       <c r="S59" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T59" t="n">
         <v>50</v>
@@ -16497,39 +16465,35 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21398,7 +21362,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>58.8</v>
+        <v>59.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -21412,7 +21376,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -21425,7 +21389,7 @@
         <v>48.9</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -21435,39 +21399,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22215,7 +22175,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -22234,7 +22194,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>56.9</v>
+        <v>56.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -22248,7 +22208,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -22261,7 +22221,7 @@
         <v>48.9</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -22271,39 +22231,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22469,24 +22425,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -22499,17 +22455,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -22518,7 +22474,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.2</v>
+        <v>56.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -22532,26 +22488,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>51.1</v>
+        <v>58.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.3</v>
+        <v>35.6</v>
       </c>
       <c r="R8" t="n">
         <v>48.9</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -22565,7 +22521,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -22603,127 +22559,127 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>102.9585</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -22749,24 +22705,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -22779,17 +22735,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -22798,7 +22754,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -22812,62 +22768,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="R9" t="n">
         <v>48.9</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>53.3</v>
+        <v>100</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22887,127 +22839,127 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9585</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -24389,27 +24341,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -24419,17 +24371,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -24438,7 +24390,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -24452,26 +24404,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>37</v>
+        <v>45.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.8</v>
+        <v>35.6</v>
       </c>
       <c r="R15" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="S15" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>44.1</v>
+        <v>32</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -24485,7 +24437,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -24506,7 +24458,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -24523,127 +24475,127 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>46.98</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -24653,12 +24605,12 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -24669,27 +24621,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -24699,17 +24651,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -24718,7 +24670,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -24732,26 +24684,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>39.3</v>
+        <v>37</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.3</v>
+        <v>38.8</v>
       </c>
       <c r="R16" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>13</v>
+        <v>44.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -24765,7 +24717,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -24786,7 +24738,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -24803,127 +24755,127 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>40.12</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>29.94</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>0.1471</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
           <t>36.4</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>26.93</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.1615</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>7.16</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -24933,12 +24885,12 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -24949,24 +24901,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -24979,17 +24931,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -24998,7 +24950,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -25012,62 +24964,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>45.1</v>
+        <v>39.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="R17" t="n">
         <v>48.9</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25087,12 +25035,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -25102,12 +25050,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -25117,97 +25065,97 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
